--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.10180165558726</v>
+        <v>1.80404276903293</v>
       </c>
       <c r="D2" t="n">
-        <v>32.62377753594021</v>
+        <v>5.301363849590284</v>
       </c>
       <c r="E2" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F2" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.67503907750949</v>
+        <v>8.884693850095292</v>
       </c>
       <c r="D3" t="n">
-        <v>54.43333131024939</v>
+        <v>8.845416337915525</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F3" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.32993005295621</v>
+        <v>5.903613633605385</v>
       </c>
       <c r="D4" t="n">
-        <v>35.65866488964064</v>
+        <v>5.794533044566604</v>
       </c>
       <c r="E4" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F4" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.41383100157753</v>
+        <v>4.779747537756348</v>
       </c>
       <c r="D5" t="n">
-        <v>29.11085833601881</v>
+        <v>4.730514479603056</v>
       </c>
       <c r="E5" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F5" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.97904751422985</v>
+        <v>6.496595221062351</v>
       </c>
       <c r="D6" t="n">
-        <v>39.99811566465088</v>
+        <v>6.499693795505768</v>
       </c>
       <c r="E6" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F6" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.37053921837725</v>
+        <v>6.885212622986304</v>
       </c>
       <c r="D7" t="n">
-        <v>41.95031871995067</v>
+        <v>6.816926791991984</v>
       </c>
       <c r="E7" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F7" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.7458233679689</v>
+        <v>4.996196297294947</v>
       </c>
       <c r="D8" t="n">
-        <v>30.59252014197792</v>
+        <v>4.971284523071413</v>
       </c>
       <c r="E8" t="n">
-        <v>12.46937827715591</v>
+        <v>2.026273970037835</v>
       </c>
       <c r="F8" t="n">
-        <v>8.084768710109962</v>
+        <v>1.313774915392869</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
